--- a/app/src/main/java/com/example/methodmesh/modules/conversions/docs/example_odk_conversion_calculate.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/conversions/docs/example_odk_conversion_calculate.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rd4b70f2c95ce4b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R70f7636b2d9046d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R0d1ab7d3a04a4877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra06c605079e04638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R4ad2c82590384618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rc3c6d59028c14a1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,8 +337,8 @@
       <x:c r="E2" s="11" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='conversion.calculate',input_category='length',return_mode='flat')</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="str"/>
-      <x:c r="G2" s="11" t="str"/>
+      <x:c r="F2" s="11"/>
+      <x:c r="G2" s="11"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -350,77 +350,75 @@
       <x:c r="C3" s="11" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="str"/>
-      <x:c r="E3" s="11" t="str"/>
+      <x:c r="D3" s="11"/>
+      <x:c r="E3" s="11"/>
       <x:c r="F3" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G3" s="11" t="str"/>
+      <x:c r="G3" s="11"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>input_from_unit</x:v>
+        <x:v>input_decimal_places</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>From unit (for example m)</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str"/>
-      <x:c r="E4" s="11" t="str"/>
-      <x:c r="F4" s="11" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="str"/>
+        <x:v>Decimal places (0–10; blank = 4)</x:v>
+      </x:c>
+      <x:c r="D4" s="11"/>
+      <x:c r="E4" s="11"/>
+      <x:c r="F4" s="11"/>
+      <x:c r="G4" s="11"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>input_to_unit</x:v>
+        <x:v>input_from_unit</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>To unit (for example km)</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str"/>
-      <x:c r="E5" s="11" t="str"/>
+        <x:v>From unit (for example m)</x:v>
+      </x:c>
+      <x:c r="D5" s="11"/>
+      <x:c r="E5" s="11"/>
       <x:c r="F5" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="G5" s="11" t="str"/>
+      <x:c r="G5" s="11"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>conversion_value</x:v>
+        <x:v>input_to_unit</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Converted value</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str"/>
-      <x:c r="E6" s="11" t="str"/>
-      <x:c r="F6" s="11" t="str"/>
-      <x:c r="G6" s="11" t="str">
+        <x:v>To unit (for example km)</x:v>
+      </x:c>
+      <x:c r="D6" s="11"/>
+      <x:c r="E6" s="11"/>
+      <x:c r="F6" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
+      <x:c r="G6" s="11"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>conversion_unit</x:v>
+        <x:v>conversion_value</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Output unit</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str"/>
-      <x:c r="E7" s="11" t="str"/>
-      <x:c r="F7" s="11" t="str"/>
+        <x:v>Converted value</x:v>
+      </x:c>
+      <x:c r="D7" s="11"/>
+      <x:c r="E7" s="11"/>
+      <x:c r="F7" s="11"/>
       <x:c r="G7" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -430,14 +428,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>conversion_summary</x:v>
+        <x:v>conversion_unit</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Summary</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str"/>
-      <x:c r="E8" s="11" t="str"/>
-      <x:c r="F8" s="11" t="str"/>
+        <x:v>Output unit</x:v>
+      </x:c>
+      <x:c r="D8" s="11"/>
+      <x:c r="E8" s="11"/>
+      <x:c r="F8" s="11"/>
       <x:c r="G8" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -447,14 +445,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>conversion_status</x:v>
+        <x:v>conversion_summary</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str"/>
-      <x:c r="E9" s="11" t="str"/>
-      <x:c r="F9" s="11" t="str"/>
+        <x:v>Summary</x:v>
+      </x:c>
+      <x:c r="D9" s="11"/>
+      <x:c r="E9" s="11"/>
+      <x:c r="F9" s="11"/>
       <x:c r="G9" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -464,31 +462,39 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>conversion_error</x:v>
+        <x:v>conversion_status</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>Error</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str"/>
-      <x:c r="E10" s="11" t="str"/>
-      <x:c r="F10" s="11" t="str"/>
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D10" s="11"/>
+      <x:c r="E10" s="11"/>
+      <x:c r="F10" s="11"/>
       <x:c r="G10" s="11" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>conversion_error</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Error</x:v>
+      </x:c>
+      <x:c r="D11" s="11"/>
+      <x:c r="E11" s="11"/>
+      <x:c r="F11" s="11"/>
+      <x:c r="G11" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
         <x:v>end_group</x:v>
       </x:c>
-      <x:c r="B11" s="11" t="str"/>
-      <x:c r="C11" s="11" t="str"/>
-      <x:c r="D11" s="11" t="str"/>
-      <x:c r="E11" s="11" t="str"/>
-      <x:c r="F11" s="11" t="str"/>
-      <x:c r="G11" s="11" t="str"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11"/>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="11"/>
       <x:c r="D12" s="11"/>

--- a/app/src/main/java/com/example/methodmesh/modules/conversions/docs/example_odk_conversion_calculate.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/conversions/docs/example_odk_conversion_calculate.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra06c605079e04638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R4ad2c82590384618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rc3c6d59028c14a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rc33d81277f0d439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rb96e2bcb2b494a71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rf1237445ab10451c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,47 +50,115 @@
     <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
   <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
 </x:styleSheet>
 </file>
 
@@ -287,15 +355,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" style="14" customWidth="1"/>
+    <x:col min="2" max="2" width="28" style="14" customWidth="1"/>
+    <x:col min="3" max="3" width="34" style="14" customWidth="1"/>
+    <x:col min="4" max="4" width="14" style="14" customWidth="1"/>
+    <x:col min="5" max="5" width="55" style="14" customWidth="1"/>
+    <x:col min="6" max="6" width="12" style="14" customWidth="1"/>
+    <x:col min="7" max="7" width="12" style="14" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -335,20 +403,20 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='conversion.calculate',input_category='length',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='conversion.calculate',input_category='length',return_mode='flat',input_payload_mode='FULL')</x:v>
       </x:c>
       <x:c r="F2" s="11"/>
       <x:c r="G2" s="11"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>decimal</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
         <x:v>input_value</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Value</x:v>
+        <x:v>Value or expression (for example 20*44)</x:v>
       </x:c>
       <x:c r="D3" s="11"/>
       <x:c r="E3" s="11"/>
@@ -411,12 +479,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>conversion_value</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Converted value</x:v>
-      </x:c>
-      <x:c r="D7" s="11"/>
+        <x:v>MethodMesh transport status</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E7" s="11"/>
       <x:c r="F7" s="11"/>
       <x:c r="G7" s="11" t="str">
@@ -428,12 +498,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>conversion_unit</x:v>
+        <x:v>conversion_value</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Output unit</x:v>
-      </x:c>
-      <x:c r="D8" s="11"/>
+        <x:v>Converted value</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E8" s="11"/>
       <x:c r="F8" s="11"/>
       <x:c r="G8" s="11" t="str">
@@ -445,12 +517,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>conversion_summary</x:v>
+        <x:v>conversion_unit</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Summary</x:v>
-      </x:c>
-      <x:c r="D9" s="11"/>
+        <x:v>Output unit / representation</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E9" s="11"/>
       <x:c r="F9" s="11"/>
       <x:c r="G9" s="11" t="str">
@@ -462,12 +536,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>conversion_status</x:v>
+        <x:v>conversion_summary</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="D10" s="11"/>
+        <x:v>Summary / working</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E10" s="11"/>
       <x:c r="F10" s="11"/>
       <x:c r="G10" s="11" t="str">
@@ -479,12 +555,14 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>conversion_error</x:v>
+        <x:v>conversion_status</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>Error</x:v>
-      </x:c>
-      <x:c r="D11" s="11"/>
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E11" s="11"/>
       <x:c r="F11" s="11"/>
       <x:c r="G11" s="11" t="str">
@@ -493,35 +571,65 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
-        <x:v>end_group</x:v>
-      </x:c>
-      <x:c r="B12" s="11"/>
-      <x:c r="C12" s="11"/>
-      <x:c r="D12" s="11"/>
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>conversion_error</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Error</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E12" s="11"/>
       <x:c r="F12" s="11"/>
-      <x:c r="G12" s="11"/>
+      <x:c r="G12" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11"/>
-      <x:c r="B13" s="11"/>
-      <x:c r="C13" s="11"/>
-      <x:c r="D13" s="11"/>
+      <x:c r="A13" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>conversion_metadata_json</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>Conversion metadata JSON</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E13" s="11"/>
       <x:c r="F13" s="11"/>
-      <x:c r="G13" s="11"/>
+      <x:c r="G13" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11"/>
-      <x:c r="B14" s="11"/>
-      <x:c r="C14" s="11"/>
-      <x:c r="D14" s="11"/>
+      <x:c r="A14" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>MethodMesh full JSON</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="E14" s="11"/>
       <x:c r="F14" s="11"/>
-      <x:c r="G14" s="11"/>
+      <x:c r="G14" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11"/>
+      <x:c r="A15" s="11" t="str">
+        <x:v>end_group</x:v>
+      </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="11"/>
       <x:c r="D15" s="11"/>
@@ -620,229 +728,229 @@
       <x:c r="G25" s="11"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="11"/>
-      <x:c r="D26" s="11"/>
-      <x:c r="E26" s="11"/>
-      <x:c r="F26" s="11"/>
-      <x:c r="G26" s="11"/>
+      <x:c r="A26" s="11" t="n"/>
+      <x:c r="B26" s="11" t="n"/>
+      <x:c r="C26" s="11" t="n"/>
+      <x:c r="D26" s="11" t="n"/>
+      <x:c r="E26" s="11" t="n"/>
+      <x:c r="F26" s="11" t="n"/>
+      <x:c r="G26" s="11" t="n"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="11"/>
-      <x:c r="D27" s="11"/>
-      <x:c r="E27" s="11"/>
-      <x:c r="F27" s="11"/>
-      <x:c r="G27" s="11"/>
+      <x:c r="A27" s="11" t="n"/>
+      <x:c r="B27" s="11" t="n"/>
+      <x:c r="C27" s="11" t="n"/>
+      <x:c r="D27" s="11" t="n"/>
+      <x:c r="E27" s="11" t="n"/>
+      <x:c r="F27" s="11" t="n"/>
+      <x:c r="G27" s="11" t="n"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="11"/>
-      <x:c r="D28" s="11"/>
-      <x:c r="E28" s="11"/>
-      <x:c r="F28" s="11"/>
-      <x:c r="G28" s="11"/>
+      <x:c r="A28" s="11" t="n"/>
+      <x:c r="B28" s="11" t="n"/>
+      <x:c r="C28" s="11" t="n"/>
+      <x:c r="D28" s="11" t="n"/>
+      <x:c r="E28" s="11" t="n"/>
+      <x:c r="F28" s="11" t="n"/>
+      <x:c r="G28" s="11" t="n"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
-      <x:c r="D29" s="11"/>
-      <x:c r="E29" s="11"/>
-      <x:c r="F29" s="11"/>
-      <x:c r="G29" s="11"/>
+      <x:c r="A29" s="11" t="n"/>
+      <x:c r="B29" s="11" t="n"/>
+      <x:c r="C29" s="11" t="n"/>
+      <x:c r="D29" s="11" t="n"/>
+      <x:c r="E29" s="11" t="n"/>
+      <x:c r="F29" s="11" t="n"/>
+      <x:c r="G29" s="11" t="n"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
-      <x:c r="D30" s="11"/>
-      <x:c r="E30" s="11"/>
-      <x:c r="F30" s="11"/>
-      <x:c r="G30" s="11"/>
+      <x:c r="A30" s="11" t="n"/>
+      <x:c r="B30" s="11" t="n"/>
+      <x:c r="C30" s="11" t="n"/>
+      <x:c r="D30" s="11" t="n"/>
+      <x:c r="E30" s="11" t="n"/>
+      <x:c r="F30" s="11" t="n"/>
+      <x:c r="G30" s="11" t="n"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
-      <x:c r="D31" s="11"/>
-      <x:c r="E31" s="11"/>
-      <x:c r="F31" s="11"/>
-      <x:c r="G31" s="11"/>
+      <x:c r="A31" s="11" t="n"/>
+      <x:c r="B31" s="11" t="n"/>
+      <x:c r="C31" s="11" t="n"/>
+      <x:c r="D31" s="11" t="n"/>
+      <x:c r="E31" s="11" t="n"/>
+      <x:c r="F31" s="11" t="n"/>
+      <x:c r="G31" s="11" t="n"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
-      <x:c r="D32" s="11"/>
-      <x:c r="E32" s="11"/>
-      <x:c r="F32" s="11"/>
-      <x:c r="G32" s="11"/>
+      <x:c r="A32" s="11" t="n"/>
+      <x:c r="B32" s="11" t="n"/>
+      <x:c r="C32" s="11" t="n"/>
+      <x:c r="D32" s="11" t="n"/>
+      <x:c r="E32" s="11" t="n"/>
+      <x:c r="F32" s="11" t="n"/>
+      <x:c r="G32" s="11" t="n"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
-      <x:c r="D33" s="11"/>
-      <x:c r="E33" s="11"/>
-      <x:c r="F33" s="11"/>
-      <x:c r="G33" s="11"/>
+      <x:c r="A33" s="11" t="n"/>
+      <x:c r="B33" s="11" t="n"/>
+      <x:c r="C33" s="11" t="n"/>
+      <x:c r="D33" s="11" t="n"/>
+      <x:c r="E33" s="11" t="n"/>
+      <x:c r="F33" s="11" t="n"/>
+      <x:c r="G33" s="11" t="n"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
-      <x:c r="D34" s="11"/>
-      <x:c r="E34" s="11"/>
-      <x:c r="F34" s="11"/>
-      <x:c r="G34" s="11"/>
+      <x:c r="A34" s="11" t="n"/>
+      <x:c r="B34" s="11" t="n"/>
+      <x:c r="C34" s="11" t="n"/>
+      <x:c r="D34" s="11" t="n"/>
+      <x:c r="E34" s="11" t="n"/>
+      <x:c r="F34" s="11" t="n"/>
+      <x:c r="G34" s="11" t="n"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
-      <x:c r="D35" s="11"/>
-      <x:c r="E35" s="11"/>
-      <x:c r="F35" s="11"/>
-      <x:c r="G35" s="11"/>
+      <x:c r="A35" s="11" t="n"/>
+      <x:c r="B35" s="11" t="n"/>
+      <x:c r="C35" s="11" t="n"/>
+      <x:c r="D35" s="11" t="n"/>
+      <x:c r="E35" s="11" t="n"/>
+      <x:c r="F35" s="11" t="n"/>
+      <x:c r="G35" s="11" t="n"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="11"/>
-      <x:c r="B36" s="11"/>
-      <x:c r="C36" s="11"/>
-      <x:c r="D36" s="11"/>
-      <x:c r="E36" s="11"/>
-      <x:c r="F36" s="11"/>
-      <x:c r="G36" s="11"/>
+      <x:c r="A36" s="11" t="n"/>
+      <x:c r="B36" s="11" t="n"/>
+      <x:c r="C36" s="11" t="n"/>
+      <x:c r="D36" s="11" t="n"/>
+      <x:c r="E36" s="11" t="n"/>
+      <x:c r="F36" s="11" t="n"/>
+      <x:c r="G36" s="11" t="n"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="11"/>
-      <x:c r="B37" s="11"/>
-      <x:c r="C37" s="11"/>
-      <x:c r="D37" s="11"/>
-      <x:c r="E37" s="11"/>
-      <x:c r="F37" s="11"/>
-      <x:c r="G37" s="11"/>
+      <x:c r="A37" s="11" t="n"/>
+      <x:c r="B37" s="11" t="n"/>
+      <x:c r="C37" s="11" t="n"/>
+      <x:c r="D37" s="11" t="n"/>
+      <x:c r="E37" s="11" t="n"/>
+      <x:c r="F37" s="11" t="n"/>
+      <x:c r="G37" s="11" t="n"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="11"/>
-      <x:c r="B38" s="11"/>
-      <x:c r="C38" s="11"/>
-      <x:c r="D38" s="11"/>
-      <x:c r="E38" s="11"/>
-      <x:c r="F38" s="11"/>
-      <x:c r="G38" s="11"/>
+      <x:c r="A38" s="11" t="n"/>
+      <x:c r="B38" s="11" t="n"/>
+      <x:c r="C38" s="11" t="n"/>
+      <x:c r="D38" s="11" t="n"/>
+      <x:c r="E38" s="11" t="n"/>
+      <x:c r="F38" s="11" t="n"/>
+      <x:c r="G38" s="11" t="n"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="11"/>
-      <x:c r="B39" s="11"/>
-      <x:c r="C39" s="11"/>
-      <x:c r="D39" s="11"/>
-      <x:c r="E39" s="11"/>
-      <x:c r="F39" s="11"/>
-      <x:c r="G39" s="11"/>
+      <x:c r="A39" s="11" t="n"/>
+      <x:c r="B39" s="11" t="n"/>
+      <x:c r="C39" s="11" t="n"/>
+      <x:c r="D39" s="11" t="n"/>
+      <x:c r="E39" s="11" t="n"/>
+      <x:c r="F39" s="11" t="n"/>
+      <x:c r="G39" s="11" t="n"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11"/>
-      <x:c r="B40" s="11"/>
-      <x:c r="C40" s="11"/>
-      <x:c r="D40" s="11"/>
-      <x:c r="E40" s="11"/>
-      <x:c r="F40" s="11"/>
-      <x:c r="G40" s="11"/>
+      <x:c r="A40" s="11" t="n"/>
+      <x:c r="B40" s="11" t="n"/>
+      <x:c r="C40" s="11" t="n"/>
+      <x:c r="D40" s="11" t="n"/>
+      <x:c r="E40" s="11" t="n"/>
+      <x:c r="F40" s="11" t="n"/>
+      <x:c r="G40" s="11" t="n"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="11"/>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="11"/>
-      <x:c r="D41" s="11"/>
-      <x:c r="E41" s="11"/>
-      <x:c r="F41" s="11"/>
-      <x:c r="G41" s="11"/>
+      <x:c r="A41" s="11" t="n"/>
+      <x:c r="B41" s="11" t="n"/>
+      <x:c r="C41" s="11" t="n"/>
+      <x:c r="D41" s="11" t="n"/>
+      <x:c r="E41" s="11" t="n"/>
+      <x:c r="F41" s="11" t="n"/>
+      <x:c r="G41" s="11" t="n"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="11"/>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="11"/>
-      <x:c r="D42" s="11"/>
-      <x:c r="E42" s="11"/>
-      <x:c r="F42" s="11"/>
-      <x:c r="G42" s="11"/>
+      <x:c r="A42" s="11" t="n"/>
+      <x:c r="B42" s="11" t="n"/>
+      <x:c r="C42" s="11" t="n"/>
+      <x:c r="D42" s="11" t="n"/>
+      <x:c r="E42" s="11" t="n"/>
+      <x:c r="F42" s="11" t="n"/>
+      <x:c r="G42" s="11" t="n"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="11"/>
-      <x:c r="B43" s="11"/>
-      <x:c r="C43" s="11"/>
-      <x:c r="D43" s="11"/>
-      <x:c r="E43" s="11"/>
-      <x:c r="F43" s="11"/>
-      <x:c r="G43" s="11"/>
+      <x:c r="A43" s="11" t="n"/>
+      <x:c r="B43" s="11" t="n"/>
+      <x:c r="C43" s="11" t="n"/>
+      <x:c r="D43" s="11" t="n"/>
+      <x:c r="E43" s="11" t="n"/>
+      <x:c r="F43" s="11" t="n"/>
+      <x:c r="G43" s="11" t="n"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="11"/>
-      <x:c r="B44" s="11"/>
-      <x:c r="C44" s="11"/>
-      <x:c r="D44" s="11"/>
-      <x:c r="E44" s="11"/>
-      <x:c r="F44" s="11"/>
-      <x:c r="G44" s="11"/>
+      <x:c r="A44" s="11" t="n"/>
+      <x:c r="B44" s="11" t="n"/>
+      <x:c r="C44" s="11" t="n"/>
+      <x:c r="D44" s="11" t="n"/>
+      <x:c r="E44" s="11" t="n"/>
+      <x:c r="F44" s="11" t="n"/>
+      <x:c r="G44" s="11" t="n"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="11"/>
-      <x:c r="B45" s="11"/>
-      <x:c r="C45" s="11"/>
-      <x:c r="D45" s="11"/>
-      <x:c r="E45" s="11"/>
-      <x:c r="F45" s="11"/>
-      <x:c r="G45" s="11"/>
+      <x:c r="A45" s="11" t="n"/>
+      <x:c r="B45" s="11" t="n"/>
+      <x:c r="C45" s="11" t="n"/>
+      <x:c r="D45" s="11" t="n"/>
+      <x:c r="E45" s="11" t="n"/>
+      <x:c r="F45" s="11" t="n"/>
+      <x:c r="G45" s="11" t="n"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="11"/>
-      <x:c r="B46" s="11"/>
-      <x:c r="C46" s="11"/>
-      <x:c r="D46" s="11"/>
-      <x:c r="E46" s="11"/>
-      <x:c r="F46" s="11"/>
-      <x:c r="G46" s="11"/>
+      <x:c r="A46" s="11" t="n"/>
+      <x:c r="B46" s="11" t="n"/>
+      <x:c r="C46" s="11" t="n"/>
+      <x:c r="D46" s="11" t="n"/>
+      <x:c r="E46" s="11" t="n"/>
+      <x:c r="F46" s="11" t="n"/>
+      <x:c r="G46" s="11" t="n"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="11"/>
-      <x:c r="B47" s="11"/>
-      <x:c r="C47" s="11"/>
-      <x:c r="D47" s="11"/>
-      <x:c r="E47" s="11"/>
-      <x:c r="F47" s="11"/>
-      <x:c r="G47" s="11"/>
+      <x:c r="A47" s="11" t="n"/>
+      <x:c r="B47" s="11" t="n"/>
+      <x:c r="C47" s="11" t="n"/>
+      <x:c r="D47" s="11" t="n"/>
+      <x:c r="E47" s="11" t="n"/>
+      <x:c r="F47" s="11" t="n"/>
+      <x:c r="G47" s="11" t="n"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="11"/>
-      <x:c r="B48" s="11"/>
-      <x:c r="C48" s="11"/>
-      <x:c r="D48" s="11"/>
-      <x:c r="E48" s="11"/>
-      <x:c r="F48" s="11"/>
-      <x:c r="G48" s="11"/>
+      <x:c r="A48" s="11" t="n"/>
+      <x:c r="B48" s="11" t="n"/>
+      <x:c r="C48" s="11" t="n"/>
+      <x:c r="D48" s="11" t="n"/>
+      <x:c r="E48" s="11" t="n"/>
+      <x:c r="F48" s="11" t="n"/>
+      <x:c r="G48" s="11" t="n"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="11"/>
-      <x:c r="B49" s="11"/>
-      <x:c r="C49" s="11"/>
-      <x:c r="D49" s="11"/>
-      <x:c r="E49" s="11"/>
-      <x:c r="F49" s="11"/>
-      <x:c r="G49" s="11"/>
+      <x:c r="A49" s="11" t="n"/>
+      <x:c r="B49" s="11" t="n"/>
+      <x:c r="C49" s="11" t="n"/>
+      <x:c r="D49" s="11" t="n"/>
+      <x:c r="E49" s="11" t="n"/>
+      <x:c r="F49" s="11" t="n"/>
+      <x:c r="G49" s="11" t="n"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="11"/>
-      <x:c r="B50" s="11"/>
-      <x:c r="C50" s="11"/>
-      <x:c r="D50" s="11"/>
-      <x:c r="E50" s="11"/>
-      <x:c r="F50" s="11"/>
-      <x:c r="G50" s="11"/>
+      <x:c r="A50" s="11" t="n"/>
+      <x:c r="B50" s="11" t="n"/>
+      <x:c r="C50" s="11" t="n"/>
+      <x:c r="D50" s="11" t="n"/>
+      <x:c r="E50" s="11" t="n"/>
+      <x:c r="F50" s="11" t="n"/>
+      <x:c r="G50" s="11" t="n"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -851,268 +959,274 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" style="14" customWidth="1"/>
+    <x:col min="2" max="2" width="22" style="14" customWidth="1"/>
+    <x:col min="3" max="3" width="22" style="14" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="10" t="str">
-        <x:v>list_name</x:v>
-      </x:c>
-      <x:c r="B1" s="10" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>label</x:v>
+      <x:c r="A1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">list_name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">label</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11"/>
-      <x:c r="B2" s="11"/>
-      <x:c r="C2" s="11"/>
+      <x:c r="A2" s="11" t="n"/>
+      <x:c r="B2" s="11" t="n"/>
+      <x:c r="C2" s="11" t="n"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11"/>
-      <x:c r="B3" s="11"/>
-      <x:c r="C3" s="11"/>
+      <x:c r="A3" s="11" t="n"/>
+      <x:c r="B3" s="11" t="n"/>
+      <x:c r="C3" s="11" t="n"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11"/>
-      <x:c r="B4" s="11"/>
-      <x:c r="C4" s="11"/>
+      <x:c r="A4" s="11" t="n"/>
+      <x:c r="B4" s="11" t="n"/>
+      <x:c r="C4" s="11" t="n"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11"/>
-      <x:c r="B5" s="11"/>
-      <x:c r="C5" s="11"/>
+      <x:c r="A5" s="11" t="n"/>
+      <x:c r="B5" s="11" t="n"/>
+      <x:c r="C5" s="11" t="n"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11"/>
-      <x:c r="B6" s="11"/>
-      <x:c r="C6" s="11"/>
+      <x:c r="A6" s="11" t="n"/>
+      <x:c r="B6" s="11" t="n"/>
+      <x:c r="C6" s="11" t="n"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11"/>
-      <x:c r="B7" s="11"/>
-      <x:c r="C7" s="11"/>
+      <x:c r="A7" s="11" t="n"/>
+      <x:c r="B7" s="11" t="n"/>
+      <x:c r="C7" s="11" t="n"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11"/>
-      <x:c r="B8" s="11"/>
-      <x:c r="C8" s="11"/>
+      <x:c r="A8" s="11" t="n"/>
+      <x:c r="B8" s="11" t="n"/>
+      <x:c r="C8" s="11" t="n"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11"/>
-      <x:c r="B9" s="11"/>
-      <x:c r="C9" s="11"/>
+      <x:c r="A9" s="11" t="n"/>
+      <x:c r="B9" s="11" t="n"/>
+      <x:c r="C9" s="11" t="n"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11"/>
-      <x:c r="B10" s="11"/>
-      <x:c r="C10" s="11"/>
+      <x:c r="A10" s="11" t="n"/>
+      <x:c r="B10" s="11" t="n"/>
+      <x:c r="C10" s="11" t="n"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11"/>
-      <x:c r="B11" s="11"/>
-      <x:c r="C11" s="11"/>
+      <x:c r="A11" s="11" t="n"/>
+      <x:c r="B11" s="11" t="n"/>
+      <x:c r="C11" s="11" t="n"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11"/>
-      <x:c r="B12" s="11"/>
-      <x:c r="C12" s="11"/>
+      <x:c r="A12" s="11" t="n"/>
+      <x:c r="B12" s="11" t="n"/>
+      <x:c r="C12" s="11" t="n"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11"/>
-      <x:c r="B13" s="11"/>
-      <x:c r="C13" s="11"/>
+      <x:c r="A13" s="11" t="n"/>
+      <x:c r="B13" s="11" t="n"/>
+      <x:c r="C13" s="11" t="n"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11"/>
-      <x:c r="B14" s="11"/>
-      <x:c r="C14" s="11"/>
+      <x:c r="A14" s="11" t="n"/>
+      <x:c r="B14" s="11" t="n"/>
+      <x:c r="C14" s="11" t="n"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11"/>
-      <x:c r="B15" s="11"/>
-      <x:c r="C15" s="11"/>
+      <x:c r="A15" s="11" t="n"/>
+      <x:c r="B15" s="11" t="n"/>
+      <x:c r="C15" s="11" t="n"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11"/>
-      <x:c r="B16" s="11"/>
-      <x:c r="C16" s="11"/>
+      <x:c r="A16" s="11" t="n"/>
+      <x:c r="B16" s="11" t="n"/>
+      <x:c r="C16" s="11" t="n"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11"/>
-      <x:c r="B17" s="11"/>
-      <x:c r="C17" s="11"/>
+      <x:c r="A17" s="11" t="n"/>
+      <x:c r="B17" s="11" t="n"/>
+      <x:c r="C17" s="11" t="n"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11"/>
-      <x:c r="B18" s="11"/>
-      <x:c r="C18" s="11"/>
+      <x:c r="A18" s="11" t="n"/>
+      <x:c r="B18" s="11" t="n"/>
+      <x:c r="C18" s="11" t="n"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11"/>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="11"/>
+      <x:c r="A19" s="11" t="n"/>
+      <x:c r="B19" s="11" t="n"/>
+      <x:c r="C19" s="11" t="n"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11"/>
-      <x:c r="B20" s="11"/>
-      <x:c r="C20" s="11"/>
+      <x:c r="A20" s="11" t="n"/>
+      <x:c r="B20" s="11" t="n"/>
+      <x:c r="C20" s="11" t="n"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="11"/>
-      <x:c r="B21" s="11"/>
-      <x:c r="C21" s="11"/>
+      <x:c r="A21" s="11" t="n"/>
+      <x:c r="B21" s="11" t="n"/>
+      <x:c r="C21" s="11" t="n"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="11"/>
-      <x:c r="B22" s="11"/>
-      <x:c r="C22" s="11"/>
+      <x:c r="A22" s="11" t="n"/>
+      <x:c r="B22" s="11" t="n"/>
+      <x:c r="C22" s="11" t="n"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="11"/>
-      <x:c r="B23" s="11"/>
-      <x:c r="C23" s="11"/>
+      <x:c r="A23" s="11" t="n"/>
+      <x:c r="B23" s="11" t="n"/>
+      <x:c r="C23" s="11" t="n"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="11"/>
-      <x:c r="B24" s="11"/>
-      <x:c r="C24" s="11"/>
+      <x:c r="A24" s="11" t="n"/>
+      <x:c r="B24" s="11" t="n"/>
+      <x:c r="C24" s="11" t="n"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="11"/>
-      <x:c r="B25" s="11"/>
-      <x:c r="C25" s="11"/>
+      <x:c r="A25" s="11" t="n"/>
+      <x:c r="B25" s="11" t="n"/>
+      <x:c r="C25" s="11" t="n"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="11"/>
+      <x:c r="A26" s="11" t="n"/>
+      <x:c r="B26" s="11" t="n"/>
+      <x:c r="C26" s="11" t="n"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="11"/>
+      <x:c r="A27" s="11" t="n"/>
+      <x:c r="B27" s="11" t="n"/>
+      <x:c r="C27" s="11" t="n"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="11"/>
+      <x:c r="A28" s="11" t="n"/>
+      <x:c r="B28" s="11" t="n"/>
+      <x:c r="C28" s="11" t="n"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
+      <x:c r="A29" s="11" t="n"/>
+      <x:c r="B29" s="11" t="n"/>
+      <x:c r="C29" s="11" t="n"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
+      <x:c r="A30" s="11" t="n"/>
+      <x:c r="B30" s="11" t="n"/>
+      <x:c r="C30" s="11" t="n"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
+      <x:c r="A31" s="11" t="n"/>
+      <x:c r="B31" s="11" t="n"/>
+      <x:c r="C31" s="11" t="n"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
+      <x:c r="A32" s="11" t="n"/>
+      <x:c r="B32" s="11" t="n"/>
+      <x:c r="C32" s="11" t="n"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
+      <x:c r="A33" s="11" t="n"/>
+      <x:c r="B33" s="11" t="n"/>
+      <x:c r="C33" s="11" t="n"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
+      <x:c r="A34" s="11" t="n"/>
+      <x:c r="B34" s="11" t="n"/>
+      <x:c r="C34" s="11" t="n"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
+      <x:c r="A35" s="11" t="n"/>
+      <x:c r="B35" s="11" t="n"/>
+      <x:c r="C35" s="11" t="n"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="11"/>
-      <x:c r="B36" s="11"/>
-      <x:c r="C36" s="11"/>
+      <x:c r="A36" s="11" t="n"/>
+      <x:c r="B36" s="11" t="n"/>
+      <x:c r="C36" s="11" t="n"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="11"/>
-      <x:c r="B37" s="11"/>
-      <x:c r="C37" s="11"/>
+      <x:c r="A37" s="11" t="n"/>
+      <x:c r="B37" s="11" t="n"/>
+      <x:c r="C37" s="11" t="n"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="11"/>
-      <x:c r="B38" s="11"/>
-      <x:c r="C38" s="11"/>
+      <x:c r="A38" s="11" t="n"/>
+      <x:c r="B38" s="11" t="n"/>
+      <x:c r="C38" s="11" t="n"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="11"/>
-      <x:c r="B39" s="11"/>
-      <x:c r="C39" s="11"/>
+      <x:c r="A39" s="11" t="n"/>
+      <x:c r="B39" s="11" t="n"/>
+      <x:c r="C39" s="11" t="n"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11"/>
-      <x:c r="B40" s="11"/>
-      <x:c r="C40" s="11"/>
+      <x:c r="A40" s="11" t="n"/>
+      <x:c r="B40" s="11" t="n"/>
+      <x:c r="C40" s="11" t="n"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="11"/>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="11"/>
+      <x:c r="A41" s="11" t="n"/>
+      <x:c r="B41" s="11" t="n"/>
+      <x:c r="C41" s="11" t="n"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="11"/>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="11"/>
+      <x:c r="A42" s="11" t="n"/>
+      <x:c r="B42" s="11" t="n"/>
+      <x:c r="C42" s="11" t="n"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="11"/>
-      <x:c r="B43" s="11"/>
-      <x:c r="C43" s="11"/>
+      <x:c r="A43" s="11" t="n"/>
+      <x:c r="B43" s="11" t="n"/>
+      <x:c r="C43" s="11" t="n"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="11"/>
-      <x:c r="B44" s="11"/>
-      <x:c r="C44" s="11"/>
+      <x:c r="A44" s="11" t="n"/>
+      <x:c r="B44" s="11" t="n"/>
+      <x:c r="C44" s="11" t="n"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="11"/>
-      <x:c r="B45" s="11"/>
-      <x:c r="C45" s="11"/>
+      <x:c r="A45" s="11" t="n"/>
+      <x:c r="B45" s="11" t="n"/>
+      <x:c r="C45" s="11" t="n"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="11"/>
-      <x:c r="B46" s="11"/>
-      <x:c r="C46" s="11"/>
+      <x:c r="A46" s="11" t="n"/>
+      <x:c r="B46" s="11" t="n"/>
+      <x:c r="C46" s="11" t="n"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="11"/>
-      <x:c r="B47" s="11"/>
-      <x:c r="C47" s="11"/>
+      <x:c r="A47" s="11" t="n"/>
+      <x:c r="B47" s="11" t="n"/>
+      <x:c r="C47" s="11" t="n"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="11"/>
-      <x:c r="B48" s="11"/>
-      <x:c r="C48" s="11"/>
+      <x:c r="A48" s="11" t="n"/>
+      <x:c r="B48" s="11" t="n"/>
+      <x:c r="C48" s="11" t="n"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="11"/>
-      <x:c r="B49" s="11"/>
-      <x:c r="C49" s="11"/>
+      <x:c r="A49" s="11" t="n"/>
+      <x:c r="B49" s="11" t="n"/>
+      <x:c r="C49" s="11" t="n"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="11"/>
-      <x:c r="B50" s="11"/>
-      <x:c r="C50" s="11"/>
+      <x:c r="A50" s="11" t="n"/>
+      <x:c r="B50" s="11" t="n"/>
+      <x:c r="C50" s="11" t="n"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1121,382 +1235,398 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" style="14" customWidth="1"/>
+    <x:col min="2" max="2" width="24" style="14" customWidth="1"/>
+    <x:col min="3" max="3" width="24" style="14" customWidth="1"/>
+    <x:col min="4" max="4" width="24" style="14" customWidth="1"/>
+    <x:col min="5" max="5" width="24" style="14" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="15" t="str">
-        <x:v>form_title</x:v>
-      </x:c>
-      <x:c r="B1" s="15" t="str">
-        <x:v>form_id</x:v>
-      </x:c>
-      <x:c r="C1" s="15" t="str">
-        <x:v>version</x:v>
-      </x:c>
-      <x:c r="D1" s="15" t="str">
-        <x:v>instance_name</x:v>
-      </x:c>
-      <x:c r="E1" s="15" t="str">
-        <x:v>default_language</x:v>
+      <x:c r="A1" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">form_title</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">form_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">version</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">instance_name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">default_language</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11" t="str">
-        <x:v>Conversion Calculate</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>conversion_calculate</x:v>
+      <x:c r="A2" s="11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Conversion Calculate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conversion_calculate</x:t>
+        </x:is>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>2026090703</x:v>
-      </x:c>
-      <x:c r="D2" s="11"/>
-      <x:c r="E2" s="11" t="str">
-        <x:v>English (en)</x:v>
+        <x:v>2026092401</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="n"/>
+      <x:c r="E2" s="11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">English (en)</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11"/>
-      <x:c r="B3" s="11"/>
-      <x:c r="C3" s="11"/>
-      <x:c r="D3" s="11"/>
-      <x:c r="E3" s="11"/>
+      <x:c r="A3" s="11" t="n"/>
+      <x:c r="B3" s="11" t="n"/>
+      <x:c r="C3" s="11" t="n"/>
+      <x:c r="D3" s="11" t="n"/>
+      <x:c r="E3" s="11" t="n"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11"/>
-      <x:c r="B4" s="11"/>
-      <x:c r="C4" s="11"/>
-      <x:c r="D4" s="11"/>
-      <x:c r="E4" s="11"/>
+      <x:c r="A4" s="11" t="n"/>
+      <x:c r="B4" s="11" t="n"/>
+      <x:c r="C4" s="11" t="n"/>
+      <x:c r="D4" s="11" t="n"/>
+      <x:c r="E4" s="11" t="n"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11"/>
-      <x:c r="B5" s="11"/>
-      <x:c r="C5" s="11"/>
-      <x:c r="D5" s="11"/>
-      <x:c r="E5" s="11"/>
+      <x:c r="A5" s="11" t="n"/>
+      <x:c r="B5" s="11" t="n"/>
+      <x:c r="C5" s="11" t="n"/>
+      <x:c r="D5" s="11" t="n"/>
+      <x:c r="E5" s="11" t="n"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11"/>
-      <x:c r="B6" s="11"/>
-      <x:c r="C6" s="11"/>
-      <x:c r="D6" s="11"/>
-      <x:c r="E6" s="11"/>
+      <x:c r="A6" s="11" t="n"/>
+      <x:c r="B6" s="11" t="n"/>
+      <x:c r="C6" s="11" t="n"/>
+      <x:c r="D6" s="11" t="n"/>
+      <x:c r="E6" s="11" t="n"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11"/>
-      <x:c r="B7" s="11"/>
-      <x:c r="C7" s="11"/>
-      <x:c r="D7" s="11"/>
-      <x:c r="E7" s="11"/>
+      <x:c r="A7" s="11" t="n"/>
+      <x:c r="B7" s="11" t="n"/>
+      <x:c r="C7" s="11" t="n"/>
+      <x:c r="D7" s="11" t="n"/>
+      <x:c r="E7" s="11" t="n"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11"/>
-      <x:c r="B8" s="11"/>
-      <x:c r="C8" s="11"/>
-      <x:c r="D8" s="11"/>
-      <x:c r="E8" s="11"/>
+      <x:c r="A8" s="11" t="n"/>
+      <x:c r="B8" s="11" t="n"/>
+      <x:c r="C8" s="11" t="n"/>
+      <x:c r="D8" s="11" t="n"/>
+      <x:c r="E8" s="11" t="n"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11"/>
-      <x:c r="B9" s="11"/>
-      <x:c r="C9" s="11"/>
-      <x:c r="D9" s="11"/>
-      <x:c r="E9" s="11"/>
+      <x:c r="A9" s="11" t="n"/>
+      <x:c r="B9" s="11" t="n"/>
+      <x:c r="C9" s="11" t="n"/>
+      <x:c r="D9" s="11" t="n"/>
+      <x:c r="E9" s="11" t="n"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11"/>
-      <x:c r="B10" s="11"/>
-      <x:c r="C10" s="11"/>
-      <x:c r="D10" s="11"/>
-      <x:c r="E10" s="11"/>
+      <x:c r="A10" s="11" t="n"/>
+      <x:c r="B10" s="11" t="n"/>
+      <x:c r="C10" s="11" t="n"/>
+      <x:c r="D10" s="11" t="n"/>
+      <x:c r="E10" s="11" t="n"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11"/>
-      <x:c r="B11" s="11"/>
-      <x:c r="C11" s="11"/>
-      <x:c r="D11" s="11"/>
-      <x:c r="E11" s="11"/>
+      <x:c r="A11" s="11" t="n"/>
+      <x:c r="B11" s="11" t="n"/>
+      <x:c r="C11" s="11" t="n"/>
+      <x:c r="D11" s="11" t="n"/>
+      <x:c r="E11" s="11" t="n"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11"/>
-      <x:c r="B12" s="11"/>
-      <x:c r="C12" s="11"/>
-      <x:c r="D12" s="11"/>
-      <x:c r="E12" s="11"/>
+      <x:c r="A12" s="11" t="n"/>
+      <x:c r="B12" s="11" t="n"/>
+      <x:c r="C12" s="11" t="n"/>
+      <x:c r="D12" s="11" t="n"/>
+      <x:c r="E12" s="11" t="n"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11"/>
-      <x:c r="B13" s="11"/>
-      <x:c r="C13" s="11"/>
-      <x:c r="D13" s="11"/>
-      <x:c r="E13" s="11"/>
+      <x:c r="A13" s="11" t="n"/>
+      <x:c r="B13" s="11" t="n"/>
+      <x:c r="C13" s="11" t="n"/>
+      <x:c r="D13" s="11" t="n"/>
+      <x:c r="E13" s="11" t="n"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11"/>
-      <x:c r="B14" s="11"/>
-      <x:c r="C14" s="11"/>
-      <x:c r="D14" s="11"/>
-      <x:c r="E14" s="11"/>
+      <x:c r="A14" s="11" t="n"/>
+      <x:c r="B14" s="11" t="n"/>
+      <x:c r="C14" s="11" t="n"/>
+      <x:c r="D14" s="11" t="n"/>
+      <x:c r="E14" s="11" t="n"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11"/>
-      <x:c r="B15" s="11"/>
-      <x:c r="C15" s="11"/>
-      <x:c r="D15" s="11"/>
-      <x:c r="E15" s="11"/>
+      <x:c r="A15" s="11" t="n"/>
+      <x:c r="B15" s="11" t="n"/>
+      <x:c r="C15" s="11" t="n"/>
+      <x:c r="D15" s="11" t="n"/>
+      <x:c r="E15" s="11" t="n"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11"/>
-      <x:c r="B16" s="11"/>
-      <x:c r="C16" s="11"/>
-      <x:c r="D16" s="11"/>
-      <x:c r="E16" s="11"/>
+      <x:c r="A16" s="11" t="n"/>
+      <x:c r="B16" s="11" t="n"/>
+      <x:c r="C16" s="11" t="n"/>
+      <x:c r="D16" s="11" t="n"/>
+      <x:c r="E16" s="11" t="n"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11"/>
-      <x:c r="B17" s="11"/>
-      <x:c r="C17" s="11"/>
-      <x:c r="D17" s="11"/>
-      <x:c r="E17" s="11"/>
+      <x:c r="A17" s="11" t="n"/>
+      <x:c r="B17" s="11" t="n"/>
+      <x:c r="C17" s="11" t="n"/>
+      <x:c r="D17" s="11" t="n"/>
+      <x:c r="E17" s="11" t="n"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11"/>
-      <x:c r="B18" s="11"/>
-      <x:c r="C18" s="11"/>
-      <x:c r="D18" s="11"/>
-      <x:c r="E18" s="11"/>
+      <x:c r="A18" s="11" t="n"/>
+      <x:c r="B18" s="11" t="n"/>
+      <x:c r="C18" s="11" t="n"/>
+      <x:c r="D18" s="11" t="n"/>
+      <x:c r="E18" s="11" t="n"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11"/>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="11"/>
-      <x:c r="D19" s="11"/>
-      <x:c r="E19" s="11"/>
+      <x:c r="A19" s="11" t="n"/>
+      <x:c r="B19" s="11" t="n"/>
+      <x:c r="C19" s="11" t="n"/>
+      <x:c r="D19" s="11" t="n"/>
+      <x:c r="E19" s="11" t="n"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11"/>
-      <x:c r="B20" s="11"/>
-      <x:c r="C20" s="11"/>
-      <x:c r="D20" s="11"/>
-      <x:c r="E20" s="11"/>
+      <x:c r="A20" s="11" t="n"/>
+      <x:c r="B20" s="11" t="n"/>
+      <x:c r="C20" s="11" t="n"/>
+      <x:c r="D20" s="11" t="n"/>
+      <x:c r="E20" s="11" t="n"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="11"/>
-      <x:c r="B21" s="11"/>
-      <x:c r="C21" s="11"/>
-      <x:c r="D21" s="11"/>
-      <x:c r="E21" s="11"/>
+      <x:c r="A21" s="11" t="n"/>
+      <x:c r="B21" s="11" t="n"/>
+      <x:c r="C21" s="11" t="n"/>
+      <x:c r="D21" s="11" t="n"/>
+      <x:c r="E21" s="11" t="n"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="11"/>
-      <x:c r="B22" s="11"/>
-      <x:c r="C22" s="11"/>
-      <x:c r="D22" s="11"/>
-      <x:c r="E22" s="11"/>
+      <x:c r="A22" s="11" t="n"/>
+      <x:c r="B22" s="11" t="n"/>
+      <x:c r="C22" s="11" t="n"/>
+      <x:c r="D22" s="11" t="n"/>
+      <x:c r="E22" s="11" t="n"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="11"/>
-      <x:c r="B23" s="11"/>
-      <x:c r="C23" s="11"/>
-      <x:c r="D23" s="11"/>
-      <x:c r="E23" s="11"/>
+      <x:c r="A23" s="11" t="n"/>
+      <x:c r="B23" s="11" t="n"/>
+      <x:c r="C23" s="11" t="n"/>
+      <x:c r="D23" s="11" t="n"/>
+      <x:c r="E23" s="11" t="n"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="11"/>
-      <x:c r="B24" s="11"/>
-      <x:c r="C24" s="11"/>
-      <x:c r="D24" s="11"/>
-      <x:c r="E24" s="11"/>
+      <x:c r="A24" s="11" t="n"/>
+      <x:c r="B24" s="11" t="n"/>
+      <x:c r="C24" s="11" t="n"/>
+      <x:c r="D24" s="11" t="n"/>
+      <x:c r="E24" s="11" t="n"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="11"/>
-      <x:c r="B25" s="11"/>
-      <x:c r="C25" s="11"/>
-      <x:c r="D25" s="11"/>
-      <x:c r="E25" s="11"/>
+      <x:c r="A25" s="11" t="n"/>
+      <x:c r="B25" s="11" t="n"/>
+      <x:c r="C25" s="11" t="n"/>
+      <x:c r="D25" s="11" t="n"/>
+      <x:c r="E25" s="11" t="n"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="11"/>
-      <x:c r="D26" s="11"/>
-      <x:c r="E26" s="11"/>
+      <x:c r="A26" s="11" t="n"/>
+      <x:c r="B26" s="11" t="n"/>
+      <x:c r="C26" s="11" t="n"/>
+      <x:c r="D26" s="11" t="n"/>
+      <x:c r="E26" s="11" t="n"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="11"/>
-      <x:c r="D27" s="11"/>
-      <x:c r="E27" s="11"/>
+      <x:c r="A27" s="11" t="n"/>
+      <x:c r="B27" s="11" t="n"/>
+      <x:c r="C27" s="11" t="n"/>
+      <x:c r="D27" s="11" t="n"/>
+      <x:c r="E27" s="11" t="n"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="11"/>
-      <x:c r="D28" s="11"/>
-      <x:c r="E28" s="11"/>
+      <x:c r="A28" s="11" t="n"/>
+      <x:c r="B28" s="11" t="n"/>
+      <x:c r="C28" s="11" t="n"/>
+      <x:c r="D28" s="11" t="n"/>
+      <x:c r="E28" s="11" t="n"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
-      <x:c r="D29" s="11"/>
-      <x:c r="E29" s="11"/>
+      <x:c r="A29" s="11" t="n"/>
+      <x:c r="B29" s="11" t="n"/>
+      <x:c r="C29" s="11" t="n"/>
+      <x:c r="D29" s="11" t="n"/>
+      <x:c r="E29" s="11" t="n"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
-      <x:c r="D30" s="11"/>
-      <x:c r="E30" s="11"/>
+      <x:c r="A30" s="11" t="n"/>
+      <x:c r="B30" s="11" t="n"/>
+      <x:c r="C30" s="11" t="n"/>
+      <x:c r="D30" s="11" t="n"/>
+      <x:c r="E30" s="11" t="n"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
-      <x:c r="D31" s="11"/>
-      <x:c r="E31" s="11"/>
+      <x:c r="A31" s="11" t="n"/>
+      <x:c r="B31" s="11" t="n"/>
+      <x:c r="C31" s="11" t="n"/>
+      <x:c r="D31" s="11" t="n"/>
+      <x:c r="E31" s="11" t="n"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
-      <x:c r="D32" s="11"/>
-      <x:c r="E32" s="11"/>
+      <x:c r="A32" s="11" t="n"/>
+      <x:c r="B32" s="11" t="n"/>
+      <x:c r="C32" s="11" t="n"/>
+      <x:c r="D32" s="11" t="n"/>
+      <x:c r="E32" s="11" t="n"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
-      <x:c r="D33" s="11"/>
-      <x:c r="E33" s="11"/>
+      <x:c r="A33" s="11" t="n"/>
+      <x:c r="B33" s="11" t="n"/>
+      <x:c r="C33" s="11" t="n"/>
+      <x:c r="D33" s="11" t="n"/>
+      <x:c r="E33" s="11" t="n"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
-      <x:c r="D34" s="11"/>
-      <x:c r="E34" s="11"/>
+      <x:c r="A34" s="11" t="n"/>
+      <x:c r="B34" s="11" t="n"/>
+      <x:c r="C34" s="11" t="n"/>
+      <x:c r="D34" s="11" t="n"/>
+      <x:c r="E34" s="11" t="n"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
-      <x:c r="D35" s="11"/>
-      <x:c r="E35" s="11"/>
+      <x:c r="A35" s="11" t="n"/>
+      <x:c r="B35" s="11" t="n"/>
+      <x:c r="C35" s="11" t="n"/>
+      <x:c r="D35" s="11" t="n"/>
+      <x:c r="E35" s="11" t="n"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="11"/>
-      <x:c r="B36" s="11"/>
-      <x:c r="C36" s="11"/>
-      <x:c r="D36" s="11"/>
-      <x:c r="E36" s="11"/>
+      <x:c r="A36" s="11" t="n"/>
+      <x:c r="B36" s="11" t="n"/>
+      <x:c r="C36" s="11" t="n"/>
+      <x:c r="D36" s="11" t="n"/>
+      <x:c r="E36" s="11" t="n"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="11"/>
-      <x:c r="B37" s="11"/>
-      <x:c r="C37" s="11"/>
-      <x:c r="D37" s="11"/>
-      <x:c r="E37" s="11"/>
+      <x:c r="A37" s="11" t="n"/>
+      <x:c r="B37" s="11" t="n"/>
+      <x:c r="C37" s="11" t="n"/>
+      <x:c r="D37" s="11" t="n"/>
+      <x:c r="E37" s="11" t="n"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="11"/>
-      <x:c r="B38" s="11"/>
-      <x:c r="C38" s="11"/>
-      <x:c r="D38" s="11"/>
-      <x:c r="E38" s="11"/>
+      <x:c r="A38" s="11" t="n"/>
+      <x:c r="B38" s="11" t="n"/>
+      <x:c r="C38" s="11" t="n"/>
+      <x:c r="D38" s="11" t="n"/>
+      <x:c r="E38" s="11" t="n"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="11"/>
-      <x:c r="B39" s="11"/>
-      <x:c r="C39" s="11"/>
-      <x:c r="D39" s="11"/>
-      <x:c r="E39" s="11"/>
+      <x:c r="A39" s="11" t="n"/>
+      <x:c r="B39" s="11" t="n"/>
+      <x:c r="C39" s="11" t="n"/>
+      <x:c r="D39" s="11" t="n"/>
+      <x:c r="E39" s="11" t="n"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11"/>
-      <x:c r="B40" s="11"/>
-      <x:c r="C40" s="11"/>
-      <x:c r="D40" s="11"/>
-      <x:c r="E40" s="11"/>
+      <x:c r="A40" s="11" t="n"/>
+      <x:c r="B40" s="11" t="n"/>
+      <x:c r="C40" s="11" t="n"/>
+      <x:c r="D40" s="11" t="n"/>
+      <x:c r="E40" s="11" t="n"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="11"/>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="11"/>
-      <x:c r="D41" s="11"/>
-      <x:c r="E41" s="11"/>
+      <x:c r="A41" s="11" t="n"/>
+      <x:c r="B41" s="11" t="n"/>
+      <x:c r="C41" s="11" t="n"/>
+      <x:c r="D41" s="11" t="n"/>
+      <x:c r="E41" s="11" t="n"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="11"/>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="11"/>
-      <x:c r="D42" s="11"/>
-      <x:c r="E42" s="11"/>
+      <x:c r="A42" s="11" t="n"/>
+      <x:c r="B42" s="11" t="n"/>
+      <x:c r="C42" s="11" t="n"/>
+      <x:c r="D42" s="11" t="n"/>
+      <x:c r="E42" s="11" t="n"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="11"/>
-      <x:c r="B43" s="11"/>
-      <x:c r="C43" s="11"/>
-      <x:c r="D43" s="11"/>
-      <x:c r="E43" s="11"/>
+      <x:c r="A43" s="11" t="n"/>
+      <x:c r="B43" s="11" t="n"/>
+      <x:c r="C43" s="11" t="n"/>
+      <x:c r="D43" s="11" t="n"/>
+      <x:c r="E43" s="11" t="n"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="11"/>
-      <x:c r="B44" s="11"/>
-      <x:c r="C44" s="11"/>
-      <x:c r="D44" s="11"/>
-      <x:c r="E44" s="11"/>
+      <x:c r="A44" s="11" t="n"/>
+      <x:c r="B44" s="11" t="n"/>
+      <x:c r="C44" s="11" t="n"/>
+      <x:c r="D44" s="11" t="n"/>
+      <x:c r="E44" s="11" t="n"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="11"/>
-      <x:c r="B45" s="11"/>
-      <x:c r="C45" s="11"/>
-      <x:c r="D45" s="11"/>
-      <x:c r="E45" s="11"/>
+      <x:c r="A45" s="11" t="n"/>
+      <x:c r="B45" s="11" t="n"/>
+      <x:c r="C45" s="11" t="n"/>
+      <x:c r="D45" s="11" t="n"/>
+      <x:c r="E45" s="11" t="n"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="11"/>
-      <x:c r="B46" s="11"/>
-      <x:c r="C46" s="11"/>
-      <x:c r="D46" s="11"/>
-      <x:c r="E46" s="11"/>
+      <x:c r="A46" s="11" t="n"/>
+      <x:c r="B46" s="11" t="n"/>
+      <x:c r="C46" s="11" t="n"/>
+      <x:c r="D46" s="11" t="n"/>
+      <x:c r="E46" s="11" t="n"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="11"/>
-      <x:c r="B47" s="11"/>
-      <x:c r="C47" s="11"/>
-      <x:c r="D47" s="11"/>
-      <x:c r="E47" s="11"/>
+      <x:c r="A47" s="11" t="n"/>
+      <x:c r="B47" s="11" t="n"/>
+      <x:c r="C47" s="11" t="n"/>
+      <x:c r="D47" s="11" t="n"/>
+      <x:c r="E47" s="11" t="n"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="11"/>
-      <x:c r="B48" s="11"/>
-      <x:c r="C48" s="11"/>
-      <x:c r="D48" s="11"/>
-      <x:c r="E48" s="11"/>
+      <x:c r="A48" s="11" t="n"/>
+      <x:c r="B48" s="11" t="n"/>
+      <x:c r="C48" s="11" t="n"/>
+      <x:c r="D48" s="11" t="n"/>
+      <x:c r="E48" s="11" t="n"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="11"/>
-      <x:c r="B49" s="11"/>
-      <x:c r="C49" s="11"/>
-      <x:c r="D49" s="11"/>
-      <x:c r="E49" s="11"/>
+      <x:c r="A49" s="11" t="n"/>
+      <x:c r="B49" s="11" t="n"/>
+      <x:c r="C49" s="11" t="n"/>
+      <x:c r="D49" s="11" t="n"/>
+      <x:c r="E49" s="11" t="n"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="11"/>
-      <x:c r="B50" s="11"/>
-      <x:c r="C50" s="11"/>
-      <x:c r="D50" s="11"/>
-      <x:c r="E50" s="11"/>
+      <x:c r="A50" s="11" t="n"/>
+      <x:c r="B50" s="11" t="n"/>
+      <x:c r="C50" s="11" t="n"/>
+      <x:c r="D50" s="11" t="n"/>
+      <x:c r="E50" s="11" t="n"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
